--- a/bugs/reporte_bugs.xlsx
+++ b/bugs/reporte_bugs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\OneDrive\Escritorio\QA\ProyectoFinal-BelenFn\bugs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE4A6E-F37F-4409-8FF1-F46ED43C72C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97276CE7-A0A2-45CA-928D-2EB9F3E8559A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
